--- a/tests/fixtures/synthetic_ddr_golden_a.xlsx
+++ b/tests/fixtures/synthetic_ddr_golden_a.xlsx
@@ -23021,7 +23021,7 @@
       </c>
       <c r="M52" s="1038"/>
       <c r="N52" s="1038">
-        <v>1515041004</v>
+        <v>1000000001</v>
       </c>
       <c r="O52" s="1038"/>
       <c r="P52" s="1039">
@@ -23061,7 +23061,7 @@
       </c>
       <c r="M53" s="1038"/>
       <c r="N53" s="1038">
-        <v>15013006</v>
+        <v>10000002</v>
       </c>
       <c r="O53" s="1038"/>
       <c r="P53" s="1039">
